--- a/artfynd/A 14936-2020 artfynd.xlsx
+++ b/artfynd/A 14936-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14936-2020 artfynd.xlsx
+++ b/artfynd/A 14936-2020 artfynd.xlsx
@@ -1182,7 +1182,7 @@
         <v>117846280</v>
       </c>
       <c r="B6" t="n">
-        <v>57207</v>
+        <v>57208</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14936-2020 artfynd.xlsx
+++ b/artfynd/A 14936-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1300,6 +1300,134 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125165809</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56725</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Anders-Ersabodarna, Fyrås, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>514876</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7043593</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>04:04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>04:04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14936-2020 artfynd.xlsx
+++ b/artfynd/A 14936-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,6 +1429,130 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125456140</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56965</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Anders-Ersabodarna, Fyrås, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>514876</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7043593</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14936-2020 artfynd.xlsx
+++ b/artfynd/A 14936-2020 artfynd.xlsx
@@ -1306,7 +1306,7 @@
         <v>125165809</v>
       </c>
       <c r="B7" t="n">
-        <v>56725</v>
+        <v>56839</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>125456140</v>
       </c>
       <c r="B8" t="n">
-        <v>56965</v>
+        <v>57053</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 14936-2020 artfynd.xlsx
+++ b/artfynd/A 14936-2020 artfynd.xlsx
@@ -1429,7 +1429,7 @@
         <v>125456140</v>
       </c>
       <c r="B8" t="n">
-        <v>57063</v>
+        <v>57064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
